--- a/feedback_surveys/041_gym_social_media_campaign_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/041_gym_social_media_campaign_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What do you know about our social media campaign?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please tell us about your current understanding of our social media presence.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>campaign_impressions</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,7 +555,11 @@
           <t>What are your impressions of our latest social media campaign?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Be as specific as possible in your description.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,7 +582,11 @@
           <t>Which of the following best describes your experience with our campaign?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>campaign_relevance</t>
+          <t>relevance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,7 +609,11 @@
           <t>How relevant do you think our social media campaign is to our brand?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose one that best fits.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>campaign_liking</t>
+          <t>liking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,7 +636,11 @@
           <t>How much do you like our social media campaign?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Choose one that best fits.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>campaign_liking_2</t>
+          <t>campaign_impressions_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How much do you like our social media campaign?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are your impressions of our social media campaign?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Be as specific as possible in your description.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>campaign_engagement_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you have any additional comments?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Campaign Engagement 2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -686,10 +714,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>We will only use this for survey follow-ups.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Optional, but helpful for follow-ups.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>We will use this for future reference.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your job title?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>For our records.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Do you have any additional comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>We value your input and would love to hear more.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What would you like to see more of from our social media campaign?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Your input will help shape future campaigns.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Do you have any other comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>We appreciate your input.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What would you like to see more of?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Email 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>We will only use this for survey follow-ups.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Do you have any other comments or suggestions?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Phone 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Optional, but helpful for follow-ups.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Name 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>For our records.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Job Title 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>For our records.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -934,15 +1006,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>What is your department?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>For our records.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -957,131 +1033,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>company_2</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>What is your role?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>For our records.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>job_title_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>department_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>role_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>campaign_impressions_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What are your impressions of our latest social media campaign?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>campaign_engagement_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Which of the following best describes your experience with our campaign?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1063,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1096,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'not_engaging'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Not engaging'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1113,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_engaging'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat engaging'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,216 +1130,165 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'very_engaging'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Very engaging'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>campaign_relevance_choices</t>
+          <t>relevance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'not_relevant_at_all'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Not relevant at all'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>campaign_relevance_choices</t>
+          <t>relevance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_relevant'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat relevant'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>campaign_relevance_choices</t>
+          <t>relevance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'very_relevant'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Very relevant'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>campaign_liking_choices</t>
+          <t>liking_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'not_at_all'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Not at all'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>campaign_liking_choices</t>
+          <t>liking_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>campaign_liking_choices</t>
+          <t>liking_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'very_much'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Very much'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>campaign_liking_2_choices</t>
+          <t>campaign_engagement_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'not_at_all'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Not at all'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>campaign_liking_2_choices</t>
+          <t>campaign_engagement_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>campaign_liking_2_choices</t>
+          <t>campaign_engagement_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'very_much'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Very much'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>campaign_engagement_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'option':_'not_engaging'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'option': 'Not engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>campaign_engagement_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'option':_'somewhat_engaging'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'option': 'Somewhat engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>campaign_engagement_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'option':_'very_engaging'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'option': 'Very engaging'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
